--- a/artfynd/A 7038-2023 artfynd.xlsx
+++ b/artfynd/A 7038-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7038-2023 artfynd.xlsx
+++ b/artfynd/A 7038-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>105036400</v>
       </c>
       <c r="B2" t="n">
-        <v>78000</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701248.8278660057</v>
+        <v>701249</v>
       </c>
       <c r="R2" t="n">
-        <v>6363507.659760545</v>
+        <v>6363507</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105036438</v>
+        <v>105036363</v>
       </c>
       <c r="B3" t="n">
-        <v>73554</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229477</v>
+        <v>1026</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blemlavsklotter</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phacographa zwackhii</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.massal ex Zwackh) Hafellner</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701272.7962956061</v>
+        <v>701389</v>
       </c>
       <c r="R3" t="n">
-        <v>6363537.468056167</v>
+        <v>6363584</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105036421</v>
+        <v>105036364</v>
       </c>
       <c r="B4" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230185</v>
+        <v>1026</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701302.7293123305</v>
+        <v>701364</v>
       </c>
       <c r="R4" t="n">
-        <v>6363534.081286011</v>
+        <v>6363584</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105036429</v>
+        <v>105036366</v>
       </c>
       <c r="B5" t="n">
-        <v>77412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229183</v>
+        <v>1026</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Frostig asplav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lecidella laureri</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hepp) Körb.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701370.0918323097</v>
+        <v>701390</v>
       </c>
       <c r="R5" t="n">
-        <v>6363583.852730129</v>
+        <v>6363572</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105036434</v>
+        <v>105036367</v>
       </c>
       <c r="B6" t="n">
-        <v>42760</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101242</v>
+        <v>1026</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701256.8997776117</v>
+        <v>701373</v>
       </c>
       <c r="R6" t="n">
-        <v>6363508.597467141</v>
+        <v>6363572</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105036367</v>
+        <v>105036427</v>
       </c>
       <c r="B7" t="n">
-        <v>77998</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1026</v>
+        <v>2779</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701373.3754793993</v>
+        <v>701319</v>
       </c>
       <c r="R7" t="n">
-        <v>6363572.131461475</v>
+        <v>6363656</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105036364</v>
+        <v>105036434</v>
       </c>
       <c r="B8" t="n">
-        <v>77998</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1026</v>
+        <v>101242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701364.1530750293</v>
+        <v>701257</v>
       </c>
       <c r="R8" t="n">
-        <v>6363583.560060237</v>
+        <v>6363508</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,6 +1375,612 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>105036429</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79238</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229183</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Frostig asplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lecidella laureri</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hepp) Körb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gajstmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>701370</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6363584</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105036430</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79238</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229183</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Frostig asplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lecidella laureri</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hepp) Körb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gajstmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>701206</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6363464</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105036438</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75348</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229477</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blemlavsklotter</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phacographa zwackhii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(A.massal ex Zwackh) Hafellner</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gajstmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>701272</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6363538</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105036421</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gajstmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>701302</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6363534</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105036422</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gajstmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>701212</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6363467</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>105036439</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80648</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>257108</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tät korallorangelav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Blastenia coralliza</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Arup &amp; Åkelius) Arup et al.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gajstmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>701323</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6363654</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>

--- a/artfynd/A 7038-2023 artfynd.xlsx
+++ b/artfynd/A 7038-2023 artfynd.xlsx
@@ -1890,7 +1890,7 @@
         <v>105036439</v>
       </c>
       <c r="B14" t="n">
-        <v>80648</v>
+        <v>80694</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 7038-2023 artfynd.xlsx
+++ b/artfynd/A 7038-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036400</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036363</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036364</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036366</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036367</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036427</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036434</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036429</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036430</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036438</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036421</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036422</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,8 +2050,28 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036439</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>